--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post FET_HRM-2031-0232/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Back_Summary.xlsx
@@ -434,12 +434,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -451,23 +446,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.2897</v>
+        <v>17.71668</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76556</v>
+        <v>17.28415</v>
       </c>
       <c r="E2" t="n">
-        <v>17.45726</v>
+        <v>17.39609</v>
       </c>
       <c r="F2" t="n">
-        <v>22.61672</v>
+        <v>44.96682</v>
       </c>
       <c r="G2" t="n">
-        <v>34.94094</v>
+        <v>0.05285</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.90666</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +475,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.81145</v>
+        <v>17.75408</v>
       </c>
       <c r="D3" t="n">
-        <v>16.63098</v>
+        <v>17.5275</v>
       </c>
       <c r="E3" t="n">
-        <v>17.28205</v>
+        <v>17.62791</v>
       </c>
       <c r="F3" t="n">
-        <v>22.93421</v>
+        <v>45.33681</v>
       </c>
       <c r="G3" t="n">
-        <v>35.87424</v>
+        <v>0.05353</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.91417</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +500,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.29219</v>
+        <v>17.64358</v>
       </c>
       <c r="D4" t="n">
-        <v>16.2537</v>
+        <v>17.3507</v>
       </c>
       <c r="E4" t="n">
-        <v>17.37811</v>
+        <v>17.41707</v>
       </c>
       <c r="F4" t="n">
-        <v>22.58914</v>
+        <v>44.69962</v>
       </c>
       <c r="G4" t="n">
-        <v>36.13043</v>
+        <v>0.05323</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.93653</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +525,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.1268</v>
+        <v>17.60867</v>
       </c>
       <c r="D5" t="n">
-        <v>16.35431</v>
+        <v>17.17182</v>
       </c>
       <c r="E5" t="n">
-        <v>17.47205</v>
+        <v>17.36104</v>
       </c>
       <c r="F5" t="n">
-        <v>22.46823</v>
+        <v>45.0321</v>
       </c>
       <c r="G5" t="n">
-        <v>35.94771</v>
+        <v>0.05289</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.91794</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +550,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.26742</v>
+        <v>17.72182</v>
       </c>
       <c r="D6" t="n">
-        <v>17.16186</v>
+        <v>17.67858</v>
       </c>
       <c r="E6" t="n">
-        <v>17.24793</v>
+        <v>17.70175</v>
       </c>
       <c r="F6" t="n">
-        <v>22.38447</v>
+        <v>45.05919</v>
       </c>
       <c r="G6" t="n">
-        <v>35.84831</v>
+        <v>0.05344</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.92101</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +575,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.26649</v>
+        <v>17.85926</v>
       </c>
       <c r="D7" t="n">
-        <v>17.05692</v>
+        <v>17.3772</v>
       </c>
       <c r="E7" t="n">
-        <v>17.16237</v>
+        <v>17.67618</v>
       </c>
       <c r="F7" t="n">
-        <v>22.05604</v>
+        <v>44.3725</v>
       </c>
       <c r="G7" t="n">
-        <v>36.58491</v>
+        <v>0.05393</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.91875</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +600,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.63042</v>
+        <v>17.55283</v>
       </c>
       <c r="D8" t="n">
-        <v>17.02038</v>
+        <v>17.37793</v>
       </c>
       <c r="E8" t="n">
-        <v>17.28671</v>
+        <v>17.48824</v>
       </c>
       <c r="F8" t="n">
-        <v>22.58223</v>
+        <v>44.84271</v>
       </c>
       <c r="G8" t="n">
-        <v>36.41128</v>
+        <v>0.05235</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.90345</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +625,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.62213</v>
+        <v>17.88955</v>
       </c>
       <c r="D9" t="n">
-        <v>16.59527</v>
+        <v>17.47931</v>
       </c>
       <c r="E9" t="n">
-        <v>17.16144</v>
+        <v>17.69975</v>
       </c>
       <c r="F9" t="n">
-        <v>22.90277</v>
+        <v>44.33772</v>
       </c>
       <c r="G9" t="n">
-        <v>34.78662</v>
+        <v>0.05349</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.88878</v>
       </c>
     </row>
     <row r="10">
@@ -631,48 +650,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.46049</v>
+        <v>17.87025</v>
       </c>
       <c r="D10" t="n">
-        <v>16.61744</v>
+        <v>17.32351</v>
       </c>
       <c r="E10" t="n">
-        <v>17.15967</v>
+        <v>17.79773</v>
       </c>
       <c r="F10" t="n">
-        <v>22.65618</v>
+        <v>44.2852</v>
       </c>
       <c r="G10" t="n">
-        <v>35.03313</v>
+        <v>0.05265</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.91948</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -686,26 +688,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.65866</v>
+        <v>0.64186</v>
       </c>
       <c r="D12" t="n">
-        <v>17.44972</v>
-      </c>
-      <c r="E12" t="n">
-        <v>18.02035</v>
-      </c>
-      <c r="F12" t="n">
-        <v>45.12237</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05306</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.88522</v>
+        <v>1.15842</v>
       </c>
     </row>
     <row r="13">
@@ -715,22 +705,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.57313</v>
+        <v>0.62674</v>
       </c>
       <c r="D13" t="n">
-        <v>17.38165</v>
-      </c>
-      <c r="E13" t="n">
-        <v>17.07968</v>
-      </c>
-      <c r="F13" t="n">
-        <v>44.46734</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05341</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.93508</v>
+        <v>1.17861</v>
       </c>
     </row>
     <row r="14">
@@ -740,22 +718,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.74972</v>
+        <v>0.61979</v>
       </c>
       <c r="D14" t="n">
-        <v>17.27131</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.2765</v>
-      </c>
-      <c r="F14" t="n">
-        <v>43.95704</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05325</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.92173</v>
+        <v>1.17021</v>
       </c>
     </row>
     <row r="15">
@@ -765,22 +731,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.65497</v>
+        <v>0.62846</v>
       </c>
       <c r="D15" t="n">
-        <v>17.51167</v>
-      </c>
-      <c r="E15" t="n">
-        <v>17.37532</v>
-      </c>
-      <c r="F15" t="n">
-        <v>44.79846</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05337</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.87987</v>
+        <v>1.19474</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +744,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.83341</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>17.4204</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.48057</v>
-      </c>
-      <c r="F16" t="n">
-        <v>44.60333</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05264</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.90762</v>
+        <v>1.17998</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +757,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.39634</v>
+        <v>0.63536</v>
       </c>
       <c r="D17" t="n">
-        <v>17.16345</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17.15163</v>
-      </c>
-      <c r="F17" t="n">
-        <v>45.44577</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05192</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.87069</v>
+        <v>1.17704</v>
       </c>
     </row>
     <row r="18">
@@ -840,22 +770,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.77385</v>
+        <v>0.64194</v>
       </c>
       <c r="D18" t="n">
-        <v>17.41982</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.32404</v>
-      </c>
-      <c r="F18" t="n">
-        <v>45.33481</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05264</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.88886</v>
+        <v>1.16791</v>
       </c>
     </row>
     <row r="19">
@@ -865,22 +783,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.53088</v>
+        <v>0.63664</v>
       </c>
       <c r="D19" t="n">
-        <v>17.33032</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.5801</v>
-      </c>
-      <c r="F19" t="n">
-        <v>43.85869</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05258</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.86528</v>
+        <v>1.16757</v>
       </c>
     </row>
     <row r="20">
@@ -890,22 +796,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18.21219</v>
+        <v>0.6407</v>
       </c>
       <c r="D20" t="n">
-        <v>17.69357</v>
-      </c>
-      <c r="E20" t="n">
-        <v>17.68177</v>
-      </c>
-      <c r="F20" t="n">
-        <v>44.62847</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05208</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.91504</v>
+        <v>1.16586</v>
       </c>
     </row>
   </sheetData>
